--- a/email_log.xlsx
+++ b/email_log.xlsx
@@ -431,12 +431,12 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Timestamp</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Recipient</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -451,14 +451,14 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Message</t>
+          <t>Note</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-03-26 18:31:01</t>
+          <t>2025-03-27 21:33:51</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/email_log.xlsx
+++ b/email_log.xlsx
@@ -458,12 +458,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-03-27 21:33:51</t>
+          <t>2025-03-28 15:40:32</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>coder_akram.khan</t>
+          <t>WorkerSSal</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
